--- a/resources/dosen.xlsx
+++ b/resources/dosen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\py-skripsi akt\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRWAN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6A0532-AD35-464B-BC33-177BDD0D57FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92879840-3EC5-47D2-B8F2-FD36B8A690AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dosen Mat" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>Nama</t>
   </si>
@@ -56,9 +56,6 @@
     <t>197811112008122002</t>
   </si>
   <si>
-    <t>Dr. Putri Zahra Kamalia, S.Si., M.Si.</t>
-  </si>
-  <si>
     <t>199111142023034001</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>Prof. Dr. Drs. Zuherman Rustam, D.E.A.</t>
   </si>
   <si>
-    <t>195705221986031002</t>
-  </si>
-  <si>
     <t>Dra. Bevina Desjwiandra Handari, M.Sc., Ph.D.</t>
   </si>
   <si>
@@ -236,9 +230,6 @@
     <t>199404172018032001</t>
   </si>
   <si>
-    <t>Peter John, M.Si.</t>
-  </si>
-  <si>
     <t>030603013</t>
   </si>
   <si>
@@ -297,6 +288,15 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>03238801</t>
+  </si>
+  <si>
+    <t>Peter John, S.Si., M.Si.</t>
+  </si>
+  <si>
+    <t>Muhammad Imran, S.Si., M.Sc., Ph.D.</t>
   </si>
 </sst>
 </file>
@@ -679,26 +679,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="32.84375" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -709,7 +709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -720,7 +720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -731,7 +731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -742,95 +742,95 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -841,7 +841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -852,29 +852,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -885,7 +885,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -907,29 +907,29 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>46</v>
       </c>
@@ -940,7 +940,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>48</v>
       </c>
@@ -951,7 +951,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>50</v>
       </c>
@@ -962,7 +962,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -973,7 +973,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>54</v>
       </c>
@@ -984,7 +984,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>56</v>
       </c>
@@ -995,180 +995,169 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="2" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="2" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" s="4" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1181,13 +1170,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1195,68 +1184,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/resources/dosen.xlsx
+++ b/resources/dosen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRWAN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\py-skripsi akt\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92879840-3EC5-47D2-B8F2-FD36B8A690AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6255CF1-07F2-4A53-812E-1604FC57CB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dosen Mat" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>197402032008121001</t>
   </si>
   <si>
-    <t>Dr. Dipo Aldila, S.Si., M.Si.</t>
-  </si>
-  <si>
     <t>198803222015041003</t>
   </si>
   <si>
@@ -297,6 +294,9 @@
   </si>
   <si>
     <t>Muhammad Imran, S.Si., M.Sc., Ph.D.</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Dipo Aldila, S.Si., M.Si.</t>
   </si>
 </sst>
 </file>
@@ -680,25 +680,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="32.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -709,7 +709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -720,7 +720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -731,7 +731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -742,7 +742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -753,7 +753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -764,7 +764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -775,7 +775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -786,7 +786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -797,7 +797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -808,356 +808,356 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="2" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="B33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="2" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="B39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1170,13 +1170,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1184,68 +1184,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/resources/dosen.xlsx
+++ b/resources/dosen.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,12 +742,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>NUP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>195709211983122001</t>
+          <t>032303009</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,6 @@
       <c r="C43" t="inlineStr">
         <is>
           <t>199110162024062001</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Davi rama</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NUP</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>213123123123213</t>
         </is>
       </c>
     </row>
